--- a/Excel Practice @ Day 03 New.xlsx
+++ b/Excel Practice @ Day 03 New.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d89171c96d88985/Desktop/EXCEL1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{B01651A3-BC72-48BF-A8DB-B2F605C2C103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{752893FA-C6EC-41AD-B41D-6674C1EDC4D2}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="8_{B01651A3-BC72-48BF-A8DB-B2F605C2C103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88321FB5-61CE-4DDC-B9C6-B00FE9003BCA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,7 @@
   <definedNames>
     <definedName name="Bills">Patient_Data!$K$2:$K$41</definedName>
     <definedName name="Department">Patient_Data!$E$2:$E$41</definedName>
+    <definedName name="departments">Patient_Data!$E$2:$E$41</definedName>
     <definedName name="Dept">Patient_Data!$E$2:$E$41</definedName>
     <definedName name="Gender">Patient_Data!$D$2:$D$41</definedName>
     <definedName name="Insurance">Patient_Data!$J$2:$J$41</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="234">
   <si>
     <t>Patient_ID</t>
   </si>
@@ -982,9 +983,6 @@
       </rPr>
       <t xml:space="preserve"> then MR, NO Review</t>
     </r>
-  </si>
-  <si>
-    <t>if</t>
   </si>
   <si>
     <t>payment alert</t>
@@ -1091,7 +1089,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1127,9 +1125,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1501,34 +1496,34 @@
         <v>12</v>
       </c>
       <c r="N1" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="O1" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="R1" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="S1" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="T1" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="U1" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="V1" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="U1" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="V1" s="15" t="s">
+      <c r="W1" s="14" t="s">
         <v>233</v>
-      </c>
-      <c r="W1" s="15" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -1653,7 +1648,7 @@
         <v>8</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N42" si="0">IF(L3="pending","follow up","no action")</f>
+        <f t="shared" ref="N3:N41" si="0">IF(L3="pending","follow up","no action")</f>
         <v>no action</v>
       </c>
       <c r="O3" t="str">
@@ -4783,98 +4778,167 @@
       <c r="E48" t="s">
         <v>138</v>
       </c>
-      <c r="G48" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="49" spans="5:5">
+      <c r="G48">
+        <f>SUMIF(Department,E2,Bills)</f>
+        <v>443500</v>
+      </c>
+    </row>
+    <row r="49" spans="5:8">
       <c r="E49" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="50" spans="5:5">
+      <c r="G49">
+        <f>COUNTIF(Department,E9)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="5:8">
       <c r="E50" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="51" spans="5:5">
+      <c r="G50">
+        <f>AVERAGEIF(Department,E39,Bills)</f>
+        <v>25571.428571428572</v>
+      </c>
+    </row>
+    <row r="51" spans="5:8">
       <c r="E51" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="52" spans="5:5">
+      <c r="G51">
+        <f>SUMIF(Insurance,J40,Bills)</f>
+        <v>499500</v>
+      </c>
+    </row>
+    <row r="52" spans="5:8">
       <c r="E52" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="53" spans="5:5">
+      <c r="G52">
+        <f>COUNTIF(L2:L41,L40)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="5:8">
       <c r="E53" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="54" spans="5:5">
+      <c r="G53">
+        <f>SUMIF(L2:L41,L40,Bills)</f>
+        <v>344500</v>
+      </c>
+    </row>
+    <row r="54" spans="5:8">
       <c r="E54" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="55" spans="5:5">
+      <c r="H54">
+        <f>SUMIFS(Bills,Department,E41,Insurance,J40)</f>
+        <v>275500</v>
+      </c>
+    </row>
+    <row r="55" spans="5:8">
       <c r="E55" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="56" spans="5:5">
+      <c r="H55">
+        <f>COUNTIFS(Department,E41,L2:L41,L33)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="5:8">
       <c r="E56" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="57" spans="5:5">
+      <c r="H56">
+        <f>AVERAGEIF(Insurance,J41,Bills)</f>
+        <v>25766.666666666668</v>
+      </c>
+    </row>
+    <row r="57" spans="5:8">
       <c r="E57" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="58" spans="5:5">
+      <c r="H57">
+        <f>COUNTIF(Bills,"&gt;40000")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="5:8">
       <c r="E58" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="59" spans="5:5">
+      <c r="H58">
+        <f>SUMIF(Bills,"&gt;40000")</f>
+        <v>508000</v>
+      </c>
+    </row>
+    <row r="59" spans="5:8">
       <c r="E59" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="60" spans="5:5">
+      <c r="H59">
+        <f>COUNTIF(Stay,"&gt;5")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="5:8">
       <c r="E60" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="61" spans="5:5">
+    <row r="61" spans="5:8">
       <c r="E61" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="62" spans="5:5">
+      <c r="H61">
+        <f>SUMIFS(Bills,Department,E41,Stay,"&gt;5")</f>
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="62" spans="5:8">
       <c r="E62" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="63" spans="5:5">
+      <c r="H62">
+        <f>AVERAGEIF(L2:L41,L33,Stay)</f>
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="63" spans="5:8">
       <c r="E63" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="64" spans="5:5">
+      <c r="H63">
+        <f>_xlfn.MAXIFS(Bills,Department,E41)</f>
+        <v>76000</v>
+      </c>
+    </row>
+    <row r="64" spans="5:8">
       <c r="E64" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="65" spans="5:5">
+      <c r="H64">
+        <f>_xlfn.MINIFS(Bills,Department,E38)</f>
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="65" spans="5:8">
       <c r="E65" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="66" spans="5:5">
+      <c r="H65">
+        <f>COUNTIFS(Department,E41,L2:L41,L33)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="5:8">
       <c r="E66" t="s">
         <v>142</v>
+      </c>
+      <c r="H66">
+        <f>AVERAGEIFS(Bills,Department,E41,Insurance,J40)</f>
+        <v>55100</v>
       </c>
     </row>
   </sheetData>
